--- a/data/trans_bre/KIDM_A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_A_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 22,83</t>
+          <t>-9,6; 22,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 11,41</t>
+          <t>-15,79; 9,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 14,13</t>
+          <t>-13,74; 13,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,3</t>
+          <t>0,0; 5,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 10,17</t>
+          <t>1,39; 11,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 2,52</t>
+          <t>-5,13; 2,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,41</t>
+          <t>0,0; 10,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 0,0</t>
+          <t>-12,89; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 0,0</t>
+          <t>-11,75; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 6,09</t>
+          <t>-11,8; 6,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 1,18</t>
+          <t>-14,53; 1,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,38; -1,99</t>
+          <t>-19,88; -1,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 8,19</t>
+          <t>-9,75; 8,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 21,38</t>
+          <t>-3,52; 21,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 24,57</t>
+          <t>-7,62; 24,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 0,0</t>
+          <t>-12,08; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 0,0</t>
+          <t>-4,77; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 6,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 6,16</t>
+          <t>-4,59; 6,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 2,22</t>
+          <t>-3,58; 2,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 0,0</t>
+          <t>-8,08; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1360,22 +1360,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 3,38</t>
+          <t>-2,01; 3,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 5,09</t>
+          <t>-4,17; 4,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 0,0</t>
+          <t>-7,05; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,44</t>
+          <t>-1,41; 2,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,94</t>
+          <t>-2,99; 1,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,49</t>
+          <t>-1,84; 1,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,71</t>
+          <t>-1,92; 1,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-62,28; 238,28</t>
+          <t>-59,43; 223,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-58,81; 83,02</t>
+          <t>-62,01; 72,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-71,16; 184,35</t>
+          <t>-74,28; 166,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 318,49</t>
+          <t>-90,67; 389,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/KIDM_A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_A_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 22,36</t>
+          <t>-9,84; 22,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 9,41</t>
+          <t>-15,42; 9,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 13,86</t>
+          <t>-12,63; 12,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,98</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 11,39</t>
+          <t>1,4; 11,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 2,51</t>
+          <t>-3,88; 2,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,08</t>
+          <t>0,0; 9,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 0,0</t>
+          <t>-15,05; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 0,0</t>
+          <t>-10,84; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 6,01</t>
+          <t>-9,36; 6,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 1,41</t>
+          <t>-15,84; 0,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,88; -1,99</t>
+          <t>-19,32; -2,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 8,69</t>
+          <t>-9,99; 7,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 21,32</t>
+          <t>-3,57; 21,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 24,21</t>
+          <t>-7,99; 24,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 0,0</t>
+          <t>-15,67; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 0,0</t>
+          <t>-4,53; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,66</t>
+          <t>0,0; 5,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 6,27</t>
+          <t>-4,54; 6,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,23</t>
+          <t>-3,56; 2,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 0,0</t>
+          <t>-9,98; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,43</t>
+          <t>-2,02; 3,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 4,66</t>
+          <t>-3,59; 4,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 0,0</t>
+          <t>-7,88; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,33</t>
+          <t>-1,47; 2,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,87</t>
+          <t>-2,68; 2,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,36</t>
+          <t>-1,87; 1,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,75</t>
+          <t>-1,76; 1,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-59,43; 223,72</t>
+          <t>-58,76; 232,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-62,01; 72,51</t>
+          <t>-57,28; 84,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-74,28; 166,76</t>
+          <t>-74,95; 162,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-90,67; 389,1</t>
+          <t>-94,52; 466,48</t>
         </is>
       </c>
     </row>
